--- a/TASK.xlsx
+++ b/TASK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smntr\Desktop\IOTproject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF59890F-7EEF-4F99-A817-C65A427C3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>TASK</t>
   </si>
@@ -141,15 +141,9 @@
     <t>Alert system</t>
   </si>
   <si>
-    <t>Analitiche</t>
-  </si>
-  <si>
     <t>Broker</t>
   </si>
   <si>
-    <t>Nodered</t>
-  </si>
-  <si>
     <t>COME</t>
   </si>
   <si>
@@ -168,31 +162,203 @@
     <t>RFID</t>
   </si>
   <si>
-    <t>1. Creazione wish list (REST)
-2. publish wish list
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. subscribe wishlist idutente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. subscribe idRFID -&gt; scan con idRFID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. interroga catalog idRFID -&gt; idprodotto (REST)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4. aggiorna shopping list e wish list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5. publish payment</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. Creazione wish list (REST)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. publish wish list
 3. subscribe payment</t>
-  </si>
-  <si>
-    <t>1. subscribe wishlist idutente
-2. subscribe idRFID
-3. interroga catalog idRFID -&gt; idprodotto (REST)
-4. aggiorna shopping list e wish list
-5. publish payment</t>
-  </si>
-  <si>
-    <t>1. aggiornamento catalogo (REST)
-2. subscribe alert
-3. subscribe payment</t>
+    </r>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>1. payment, time, shopping list storichs</t>
+  </si>
+  <si>
+    <t>FARE CHECK CODE e COERENZA CODE</t>
+  </si>
+  <si>
+    <t>temperatura</t>
+  </si>
+  <si>
+    <t>max prod</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. aggiornamento catalogo (REST) -&gt; update all catalog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. subscribe alert (temperature, stocks, wherehouse)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. subscribe payment</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Script for publish ALERT</t>
+  </si>
+  <si>
+    <t>1. ALERT/PATH shelv
+2. update his movement to staff</t>
+  </si>
+  <si>
+    <t>1. ALERT low stock
+2. ALERT wrong temperature (with RASPBERRY)
+3. add max n on shelves and live temperature
+4. ALERT wherhouse</t>
+  </si>
+  <si>
+    <t>Analitiche e Nodered e thingspeak</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -218,11 +384,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,33 +678,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.06640625" customWidth="1"/>
+    <col min="2" max="2" width="15.46484375" customWidth="1"/>
+    <col min="3" max="3" width="28.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
         <v>4</v>
@@ -542,87 +717,99 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="K4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="K5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
@@ -631,34 +818,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
+    <row r="10" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
+    <row r="11" spans="1:11" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="4"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
       <c r="K11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
       <c r="K12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="J13" t="s">
         <v>17</v>
       </c>
@@ -666,17 +856,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="J16" t="s">
         <v>19</v>
       </c>
@@ -684,76 +874,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="10:11" x14ac:dyDescent="0.45">
       <c r="K17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:11" x14ac:dyDescent="0.45">
       <c r="K18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="10:11" x14ac:dyDescent="0.45">
       <c r="K19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J20" t="s">
+    <row r="22" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="J22" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K21" t="s">
+    <row r="23" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J22" t="s">
+    <row r="24" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="J24" t="s">
         <v>28</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K23" t="s">
+    <row r="25" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K24" t="s">
+    <row r="26" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K25" t="s">
+    <row r="27" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K26" t="s">
+    <row r="28" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J27" t="s">
-        <v>46</v>
-      </c>
-      <c r="K27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K28" t="s">
+    <row r="29" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="J29" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="10:11" x14ac:dyDescent="0.45">
+      <c r="K30" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TASK.xlsx
+++ b/TASK.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smntr\Desktop\IOTproject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c23260927365b9/Desktop/progetto_iot/project/IOTproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E795E9A-2416-4A4E-B7D7-1D361897C492}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1404" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -170,82 +171,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1. subscribe wishlist idutente</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2. subscribe idRFID -&gt; scan con idRFID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3. interroga catalog idRFID -&gt; idprodotto (REST)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4. aggiorna shopping list e wish list</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5. publish payment</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>1. Creazione wish list (REST)</t>
     </r>
     <r>
@@ -335,13 +260,109 @@
   </si>
   <si>
     <t>Analitiche e Nodered e thingspeak</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. subscribe wishlist idutente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. subscribe idRFID -&gt; scan con idRFID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. interroga catalog idRFID -&gt; idprodotto (REST)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4. aggiorna shopping list e wish list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5. publish payment</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +380,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -393,10 +421,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,14 +707,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.06640625" customWidth="1"/>
-    <col min="2" max="2" width="15.46484375" customWidth="1"/>
-    <col min="3" max="3" width="28.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -717,7 +745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -725,13 +753,13 @@
         <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -739,13 +767,13 @@
         <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -753,13 +781,13 @@
         <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -767,13 +795,13 @@
         <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -781,13 +809,13 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -795,13 +823,13 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -809,7 +837,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
@@ -818,37 +846,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>48</v>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
+    <row r="11" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
       <c r="K11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
         <v>17</v>
       </c>
@@ -856,17 +884,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J16" t="s">
         <v>19</v>
       </c>
@@ -874,32 +902,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.45">
-      <c r="K20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J22" t="s">
         <v>25</v>
       </c>
@@ -907,12 +935,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J24" t="s">
         <v>28</v>
       </c>
@@ -920,27 +948,27 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J29" t="s">
         <v>44</v>
       </c>
@@ -948,7 +976,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K30" t="s">
         <v>7</v>
       </c>

--- a/TASK.xlsx
+++ b/TASK.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c23260927365b9/Desktop/progetto_iot/project/IOTproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E795E9A-2416-4A4E-B7D7-1D361897C492}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B323C9-32FF-4F44-BCD1-E2612C8EFAB9}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1404" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -262,107 +261,18 @@
     <t>Analitiche e Nodered e thingspeak</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1. subscribe wishlist idutente</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2. subscribe idRFID -&gt; scan con idRFID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. interroga catalog idRFID -&gt; idprodotto (REST)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4. aggiorna shopping list e wish list</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5. publish payment</t>
-    </r>
+    <t>1. subscribe wishlist idutente
+2. subscribe idRFID -&gt; scan con idRFID
+3. interroga catalog idRFID -&gt; idprodotto (REST)
+4. aggiorna shopping list e wish list
+5. publish payment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,13 +290,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -441,6 +344,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -752,7 +659,7 @@
       <c r="B3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>56</v>
       </c>
       <c r="K3" t="s">

--- a/TASK.xlsx
+++ b/TASK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c23260927365b9/Desktop/progetto_iot/project/IOTproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B323C9-32FF-4F44-BCD1-E2612C8EFAB9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B949C61-17CA-4657-BF95-038D50D113A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,51 +211,11 @@
     <t>max prod</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1. aggiornamento catalogo (REST) -&gt; update all catalog</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. subscribe alert (temperature, stocks, wherehouse)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. subscribe payment</t>
-    </r>
-  </si>
-  <si>
     <t>1. Script for publish ALERT</t>
   </si>
   <si>
     <t>1. ALERT/PATH shelv
 2. update his movement to staff</t>
-  </si>
-  <si>
-    <t>1. ALERT low stock
-2. ALERT wrong temperature (with RASPBERRY)
-3. add max n on shelves and live temperature
-4. ALERT wherhouse</t>
   </si>
   <si>
     <t>Analitiche e Nodered e thingspeak</t>
@@ -267,12 +227,131 @@
 4. aggiorna shopping list e wish list
 5. publish payment</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. aggiornamento catalogo (REST) -&gt; update all catalog</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. subscribe alert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (temperature, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stocks, wherehouse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. subscribe payment</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. ALERT low stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. ALERT wrong temperature (with RASPBERRY)
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add max n on shelves</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and live temperature
+4. ALERT wherhouse</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,6 +369,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -660,7 +746,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -688,7 +774,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s">
         <v>9</v>
@@ -716,7 +802,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
@@ -730,7 +816,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
@@ -744,7 +830,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
@@ -755,7 +841,7 @@
     </row>
     <row r="10" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>41</v>

--- a/TASK.xlsx
+++ b/TASK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c23260927365b9/Desktop/progetto_iot/project/IOTproject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politoit-my.sharepoint.com/personal/s358011_studenti_polito_it/Documents/progetto_iot/project/IOTproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B949C61-17CA-4657-BF95-038D50D113A7}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{930FB184-FA79-4470-BF7B-F0576702F0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9355EEF-F903-4659-ABC9-D6F9D0190062}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="24" yWindow="2268" windowWidth="12504" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -214,10 +214,6 @@
     <t>1. Script for publish ALERT</t>
   </si>
   <si>
-    <t>1. ALERT/PATH shelv
-2. update his movement to staff</t>
-  </si>
-  <si>
     <t>Analitiche e Nodered e thingspeak</t>
   </si>
   <si>
@@ -343,8 +339,22 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> and live temperature
-4. ALERT wherhouse</t>
-    </r>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4. ALERT wherhouse</t>
+    </r>
+  </si>
+  <si>
+    <t>1. ALERT/PATH shelv
+2. update its movement to staff</t>
   </si>
 </sst>
 </file>
@@ -430,10 +440,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -746,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -774,7 +780,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
         <v>9</v>
@@ -802,7 +808,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
@@ -816,7 +822,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
@@ -829,7 +835,7 @@
       <c r="B9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J9" t="s">
@@ -841,7 +847,7 @@
     </row>
     <row r="10" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>41</v>
